--- a/artfynd/A 32766-2021 artfynd.xlsx
+++ b/artfynd/A 32766-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32766-2021 artfynd.xlsx
+++ b/artfynd/A 32766-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>68325472</v>
       </c>
       <c r="B2" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469644.4995030115</v>
+        <v>469644</v>
       </c>
       <c r="R2" t="n">
-        <v>6256295.759613528</v>
+        <v>6256296</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,9 @@
           <t>2017-11-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,6 +785,122 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15158748</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Nabben, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>469678</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6256132</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-08-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-08-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Litet hygge</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bertil Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bertil Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
